--- a/fixtures/xlsx/formula/input.xlsx
+++ b/fixtures/xlsx/formula/input.xlsx
@@ -2,18 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Calculations" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Double</t>
+    <t>A</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Sum</t>
   </si>
 </sst>
 </file>
@@ -23,10 +26,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -34,7 +40,10 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <f>A2*2</f>
+        <v>20</v>
+      </c>
+      <c r="C2">
+        <f>A2+B2</f>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/formula/input.xlsx
+++ b/fixtures/xlsx/formula/input.xlsx
@@ -10,13 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
+    <t>Sum</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>Sum</t>
   </si>
 </sst>
 </file>
@@ -26,13 +26,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">

--- a/fixtures/xlsx/formula/input.xlsx
+++ b/fixtures/xlsx/formula/input.xlsx
@@ -10,13 +10,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>Sum</t>
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
 </sst>
 </file>
@@ -26,13 +26,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
